--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484619_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484619_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0491</v>
+        <v>4.5236</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5997</v>
+        <v>2.5201</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4494</v>
+        <v>2.0035</v>
       </c>
       <c r="G2" t="n">
         <v>1.2823</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0575</v>
+        <v>0.417</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0098</v>
+        <v>-0.0893</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9523</v>
+        <v>0.5064</v>
       </c>
       <c r="V2" t="n">
         <v>5.3898</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7135</v>
+        <v>1.6898</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0548</v>
+        <v>1.3516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6587</v>
+        <v>0.3382</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7116</v>
+        <v>0.3671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3556</v>
+        <v>1.0657</v>
       </c>
       <c r="I4" t="n">
-        <v>2.356</v>
+        <v>-0.6986</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6507</v>
+        <v>1.7105</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1921</v>
+        <v>2.8577</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4586</v>
+        <v>-1.1472</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0609</v>
+        <v>-1.3434</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8365</v>
+        <v>-1.792</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8974</v>
+        <v>0.4486</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4417</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.043</v>
+        <v>0.5573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3987</v>
+        <v>0.171</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.89</v>
+        <v>-0.3219</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6015</v>
+        <v>1.3071</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0864</v>
+        <v>0.574</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.485</v>
+        <v>0.733</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5466</v>
+        <v>2.7116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2388</v>
+        <v>0.3556</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3078</v>
+        <v>2.356</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7479</v>
+        <v>2.6507</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2476</v>
+        <v>1.1921</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5003</v>
+        <v>1.4586</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2012</v>
+        <v>0.0609</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0088</v>
+        <v>-0.8365</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1925</v>
+        <v>0.8974</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R5" t="n">
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5888</v>
+        <v>1.0353</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7496</v>
+        <v>0.5622</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8391</v>
+        <v>0.473</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9005</v>
+        <v>-1.89</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3115</v>
+        <v>-0.6231</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1644</v>
+        <v>1.0985</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0492</v>
+        <v>2.7568</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1152</v>
+        <v>-1.6584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3671</v>
+        <v>1.5466</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0657</v>
+        <v>0.2388</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6986</v>
+        <v>1.3078</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7105</v>
+        <v>3.7479</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8577</v>
+        <v>2.2476</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1472</v>
+        <v>1.5003</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3434</v>
+        <v>-2.2012</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.792</v>
+        <v>-2.0088</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4486</v>
+        <v>-0.1925</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2029</v>
+        <v>1.0858</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2549</v>
+        <v>0.4201</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.052</v>
+        <v>0.6657</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3219</v>
+        <v>-1.9005</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9305</v>
+        <v>0.8067</v>
       </c>
       <c r="E7" t="n">
         <v>2.306</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3755</v>
+        <v>-1.4994</v>
       </c>
       <c r="G7" t="n">
         <v>1.2716</v>
@@ -1000,13 +1000,13 @@
         <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1876</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3303</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2666</v>
+        <v>0.1427</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6439</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5708</v>
+        <v>-0.2765</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3424</v>
+        <v>0.4386</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9132</v>
+        <v>-0.715</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2308</v>
@@ -1078,13 +1078,13 @@
         <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2777</v>
+        <v>0.572</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1999</v>
+        <v>0.296</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="V8" t="n">
         <v>-1.9005</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4686</v>
+        <v>-1.3324</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2026</v>
+        <v>-0.1375</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2659</v>
+        <v>-1.1949</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2511</v>
+        <v>-0.6482</v>
       </c>
       <c r="H9" t="n">
         <v>-0.7895</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4616</v>
+        <v>0.1412</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.112</v>
+        <v>1.8979</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0867</v>
+        <v>1.8206</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1987</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1391</v>
+        <v>-2.5462</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8762</v>
+        <v>-2.6101</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7371</v>
+        <v>0.064</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>0.361</v>
+        <v>-0.3622</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1818</v>
+        <v>-0.2029</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1792</v>
+        <v>-0.1593</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8759</v>
+        <v>-1.7792</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9473</v>
+        <v>-1.3399</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8232</v>
+        <v>-0.4394</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0286</v>
+        <v>-1.2511</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4485</v>
+        <v>-0.7895</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4199</v>
+        <v>-0.4616</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4652</v>
+        <v>-1.112</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5327</v>
+        <v>0.0867</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0674</v>
+        <v>-1.1987</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5633</v>
+        <v>-0.1391</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.8762</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3525</v>
+        <v>0.7371</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2296</v>
+        <v>0.0503</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1456</v>
+        <v>0.0445</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3752</v>
+        <v>0.0058</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9005</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>0.6439</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.1674</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.05</v>
+        <v>-1.9263</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6322</v>
+        <v>-1.6675</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4178</v>
+        <v>-0.2589</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6482</v>
+        <v>-1.8634</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7895</v>
+        <v>-0.6774</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1412</v>
+        <v>-1.186</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8979</v>
+        <v>-1.2604</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8206</v>
+        <v>0.0217</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.2821</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5462</v>
+        <v>-0.603</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.6101</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.064</v>
+        <v>0.0961</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0799</v>
+        <v>-0.4399</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6976</v>
+        <v>-0.106</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3823</v>
+        <v>-0.3339</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1519</v>
+        <v>-2.0405</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8187</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3332</v>
+        <v>-2.6993</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8634</v>
+        <v>-1.0286</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6774</v>
+        <v>-1.4485</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.186</v>
+        <v>0.4199</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2604</v>
+        <v>-0.4652</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0217</v>
+        <v>-0.5327</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2821</v>
+        <v>0.0674</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.603</v>
+        <v>-0.5633</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0961</v>
+        <v>0.3525</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6654</v>
+        <v>-0.3942</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2572</v>
+        <v>-0.1429</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4082</v>
+        <v>-0.2513</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0104</v>
+        <v>-1.9005</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3011</v>
+        <v>1.267</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3115</v>
+        <v>-3.1674</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3778</v>
+        <v>-2.3504</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6691</v>
+        <v>-1.5179</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7086</v>
+        <v>-0.8325</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5419</v>
@@ -1468,13 +1468,13 @@
         <v>0.5498</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1195</v>
+        <v>0.1469</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2202</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3397</v>
+        <v>0.2159</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.9475</v>
+        <v>-3.1532</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4829</v>
+        <v>-2.8125</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4646</v>
+        <v>-0.3407</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9193</v>
@@ -1546,13 +1546,13 @@
         <v>2.3823</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3933</v>
+        <v>0.1876</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2911</v>
+        <v>-0.0384</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1022</v>
+        <v>0.226</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9554</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.082999999999999</v>
+        <v>-1.532299999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>4.480799999999999</v>
+        <v>5.031099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.5637</v>
+        <v>-6.563800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>2.596399999999999</v>
+        <v>2.5964</v>
       </c>
       <c r="H15" t="n">
         <v>-7.341799999999999</v>
@@ -1615,7 +1615,7 @@
         <v>4.6463</v>
       </c>
       <c r="P15" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.99999999995449e-05</v>
       </c>
       <c r="Q15" t="n">
         <v>-18.3257</v>
@@ -1624,16 +1624,16 @@
         <v>18.3258</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2888</v>
+        <v>2.8393</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3507999999999999</v>
+        <v>0.9013</v>
       </c>
       <c r="U15" t="n">
-        <v>1.937900000000001</v>
+        <v>1.938</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.9683</v>
+        <v>-6.968299999999999</v>
       </c>
       <c r="W15" t="n">
         <v>6.386900000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6526</v>
+        <v>5.6604</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2064</v>
+        <v>4.4371</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4462</v>
+        <v>1.2232</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5027</v>
@@ -1702,13 +1702,13 @@
         <v>2.9321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2993</v>
+        <v>0.3071</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7119</v>
+        <v>-0.0573</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5874</v>
+        <v>0.3644</v>
       </c>
       <c r="V16" t="n">
         <v>4.7563</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1379</v>
+        <v>5.0286</v>
       </c>
       <c r="E17" t="n">
-        <v>5.8415</v>
+        <v>5.6492</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7036</v>
+        <v>-0.6206</v>
       </c>
       <c r="G17" t="n">
         <v>2.3524</v>
@@ -1780,13 +1780,13 @@
         <v>3.1154</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1966</v>
+        <v>0.0873</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0392</v>
+        <v>-0.2315</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2358</v>
+        <v>0.3188</v>
       </c>
       <c r="V17" t="n">
         <v>2.2224</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9031</v>
+        <v>3.8618</v>
       </c>
       <c r="E18" t="n">
-        <v>5.7969</v>
+        <v>6.1815</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8938</v>
+        <v>-2.3197</v>
       </c>
       <c r="G18" t="n">
         <v>1.596</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2977</v>
+        <v>-0.339</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8808</v>
+        <v>-0.4962</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4169</v>
+        <v>0.1572</v>
       </c>
       <c r="V18" t="n">
         <v>0.9554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7932</v>
+        <v>1.3838</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1785</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6147</v>
+        <v>0.5899</v>
       </c>
       <c r="G20" t="n">
         <v>-0.74</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7165</v>
+        <v>0.3071</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5309</v>
+        <v>0.1463</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1856</v>
+        <v>0.1608</v>
       </c>
       <c r="V20" t="n">
         <v>1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2446</v>
+        <v>-0.0173</v>
       </c>
       <c r="E21" t="n">
         <v>0.0052</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2498</v>
+        <v>-0.0225</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3392</v>
@@ -2092,13 +2092,13 @@
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4106</v>
+        <v>-0.1833</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1903</v>
+        <v>0.0369</v>
       </c>
       <c r="V21" t="n">
         <v>0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0996</v>
+        <v>-0.4979</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.021</v>
+        <v>0.1713</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0786</v>
+        <v>-0.6692</v>
       </c>
       <c r="G22" t="n">
         <v>0.2684</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6796</v>
+        <v>-0.0779</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3493</v>
+        <v>0.0601</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1607</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4328</v>
+        <v>-1.1443</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2721</v>
+        <v>0.3464</v>
       </c>
       <c r="G23" t="n">
         <v>0.8789</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5553</v>
+        <v>-0.1925</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5505</v>
+        <v>-0.2621</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0048</v>
+        <v>0.0696</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9346</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3965</v>
+        <v>-1.6312</v>
       </c>
       <c r="E24" t="n">
         <v>-3.1388</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7423</v>
+        <v>1.5076</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6375</v>
@@ -2326,13 +2326,13 @@
         <v>2.9321</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2673</v>
+        <v>0.0326</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5151</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7824</v>
+        <v>0.5477</v>
       </c>
       <c r="V24" t="n">
         <v>1.89</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1199</v>
+        <v>-2.6939</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3766</v>
+        <v>-0.6854</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2568</v>
+        <v>-2.0085</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6225</v>
+        <v>-1.2421</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2857</v>
+        <v>0.8416</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3368</v>
+        <v>-2.0837</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6896</v>
+        <v>1.263</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4492</v>
+        <v>2.5451</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2404</v>
+        <v>-1.2821</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9329</v>
+        <v>-2.5051</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8365</v>
+        <v>-1.7035</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0964</v>
+        <v>-0.8017</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8326</v>
+        <v>-1.0995</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3744</v>
+        <v>-0.7242</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1456</v>
+        <v>-0.5373</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2288</v>
+        <v>-0.1869</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3219</v>
+        <v>-1.2774</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3219</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.6395</v>
+        <v>-3.0266</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9738</v>
+        <v>-3.1843</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6656</v>
+        <v>0.1577</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.2421</v>
+        <v>-2.6225</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8416</v>
+        <v>-1.2857</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0837</v>
+        <v>-1.3368</v>
       </c>
       <c r="J26" t="n">
-        <v>1.263</v>
+        <v>-1.6896</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5451</v>
+        <v>-0.4492</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2821</v>
+        <v>-1.2404</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.5051</v>
+        <v>-0.9329</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7035</v>
+        <v>-0.8365</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8017</v>
+        <v>-0.0964</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5498</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6697</v>
+        <v>0.4676</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8258</v>
+        <v>0.3379</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.844</v>
+        <v>0.1297</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2774</v>
+        <v>-0.3219</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.6687</v>
+        <v>-5.1893</v>
       </c>
       <c r="E27" t="n">
         <v>-4.4474</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2213</v>
+        <v>-0.7419</v>
       </c>
       <c r="G27" t="n">
         <v>-1.5338</v>
@@ -2560,13 +2560,13 @@
         <v>1.6493</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5301</v>
+        <v>-0.0507</v>
       </c>
       <c r="T27" t="n">
         <v>0.0355</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5655</v>
+        <v>-0.0862</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5889</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>2.0829</v>
+        <v>4.006099999999997</v>
       </c>
       <c r="E28" t="n">
-        <v>6.563700000000003</v>
+        <v>6.563600000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.480600000000001</v>
+        <v>-2.5576</v>
       </c>
       <c r="G28" t="n">
         <v>-2.5965</v>
@@ -2638,13 +2638,13 @@
         <v>18.3257</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.2889</v>
+        <v>-0.3658999999999999</v>
       </c>
       <c r="T28" t="n">
         <v>-1.938</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3508</v>
+        <v>1.5721</v>
       </c>
       <c r="V28" t="n">
         <v>6.968300000000002</v>
@@ -2653,7 +2653,7 @@
         <v>13.3552</v>
       </c>
       <c r="X28" t="n">
-        <v>-6.386699999999999</v>
+        <v>-6.3867</v>
       </c>
     </row>
   </sheetData>
